--- a/workspace/framework_paper/edf/edf-15/edf-15_schedulables.xlsx
+++ b/workspace/framework_paper/edf/edf-15/edf-15_schedulables.xlsx
@@ -584,7 +584,7 @@
         <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -598,7 +598,7 @@
         <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -626,7 +626,7 @@
         <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -640,7 +640,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
@@ -654,7 +654,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18">
@@ -668,7 +668,7 @@
         <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19">
@@ -682,7 +682,7 @@
         <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
@@ -696,7 +696,7 @@
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -710,7 +710,7 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
